--- a/docs/PRAP_Programming_Specification_v1.31.xlsx
+++ b/docs/PRAP_Programming_Specification_v1.31.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Version_History" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Scope" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Data_Schema" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Validation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Calculation" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_UI_Spec" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Editing_IO" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Versioning" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Traceability" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Open_Points" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="00_Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="01_Version_History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_Scope" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_Data_Schema" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04_Validation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="05_Calculation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="06_UI_Spec" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="07_Editing_IO" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="08_Versioning" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="09_Traceability" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="10_Open_Points" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -718,7 +718,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    templates/PRAP_SourceData_Template_v1.6.xlsx, and sheet 03 documents the parse contract against it.</t>
+          <t xml:space="preserve">    templates/PRAP_SourceData_Template_v1.16.xlsx, and sheet 03 documents the parse contract against it.</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Template_v1.6.xlsx</t>
+          <t>templates/PRAP_SourceData_Template_v1.16.xlsx</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
@@ -4797,7 +4797,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>Documents templates/PRAP_SourceData_Template_v1.6.xlsx. Sheet and column names are matched exactly and case-sensitively.</t>
+          <t>Documents templates/PRAP_SourceData_Template_v1.16.xlsx. Sheet and column names are matched exactly and case-sensitively.</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_Programming_Specification_v1.31.xlsx
+++ b/docs/PRAP_Programming_Specification_v1.31.xlsx
@@ -4600,12 +4600,12 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>templates/PRAP_SourceData_Dummy_v1.8.xlsx</t>
+          <t>templates/PRAP_SourceData_Dummy_v1.18.xlsx</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>34 NewDrug CT + 16 Biosimilar CT + 12 'Others', 20 people, 289 assignments over 73 months.</t>
+          <t>16 NewDrug CT + 17 Biosimilar CT (Healthy) + 17 Biosimilar CT (Patient) + 12 'Others', 20 people, 277 assignments over 74 months.</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -9461,7 +9461,7 @@
     <row r="311">
       <c r="A311" s="13" t="inlineStr">
         <is>
-          <t>Plus the whole dummy dataset: running tools/verify_source_workbook.py against PRAP_SourceData_Dummy_v1.8.xlsx must give no errors and no warnings, across 62 projects, 20 people, 289 assignments and 308 periods spanning 73 months. Every period set must be contiguous, all 50 trials must carry 'Conduct (final)', 30 must also carry 'Conduct (interim)', and 12 must carry the final inspection period. No project may carry a repeated period name. Those figures are the regression baseline for Step 4.</t>
+          <t>Plus the whole dummy dataset: running tools/verify_source_workbook.py against PRAP_SourceData_Dummy_v1.18.xlsx must give no errors and no warnings, across 62 projects, 20 people, 277 assignments and 308 periods spanning 74 months. Every period set must be contiguous, all 50 trials must carry 'Conduct (final)', 30 must also carry 'Conduct (interim)', and 12 must carry the final inspection period. No project may carry a repeated period name. Those figures are the regression baseline for Step 4.</t>
         </is>
       </c>
     </row>
